--- a/4. Workspace/1. Bộ phận bảo hành/1. Thực hiện sửa chữa bảo hành/Năm 2026/Tháng 07/02. Trả bảo hành/TBH_Victory_010726.xlsx
+++ b/4. Workspace/1. Bộ phận bảo hành/1. Thực hiện sửa chữa bảo hành/Năm 2026/Tháng 07/02. Trả bảo hành/TBH_Victory_010726.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\4. Workspace\1. Bộ phận bảo hành\1. Thực hiện sửa chữa bảo hành\Năm 2026\Tháng 07\02. Trả bảo hành\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B7378B5-CB3E-490C-A016-A75318ED8A2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54678DC6-1189-432D-8DDC-ABFD9A2C2D15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -100,9 +100,6 @@
     <t>SIM + thẻ nhớ</t>
   </si>
   <si>
-    <t>Thẻ nhớ lỗi</t>
-  </si>
-  <si>
     <t>0032004C66</t>
   </si>
   <si>
@@ -113,6 +110,9 @@
   </si>
   <si>
     <t>Hà Nội, ngày 01 tháng 07 năm 2026</t>
+  </si>
+  <si>
+    <t>Thẻ nhớ lỗi, trả kèm thêm 1 thẻ nhớ bình thường lắp trong thiết bị</t>
   </si>
 </sst>
 </file>
@@ -468,6 +468,39 @@
     <xf numFmtId="49" fontId="11" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -488,39 +521,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -903,92 +903,92 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="47"/>
-      <c r="B1" s="47"/>
-      <c r="C1" s="47"/>
-      <c r="D1" s="48" t="s">
+      <c r="A1" s="40"/>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="E1" s="48"/>
-      <c r="F1" s="48"/>
-      <c r="G1" s="48"/>
-      <c r="H1" s="48"/>
-      <c r="I1" s="48"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
+      <c r="I1" s="41"/>
     </row>
     <row r="2" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="47"/>
-      <c r="B2" s="47"/>
-      <c r="C2" s="47"/>
-      <c r="D2" s="49" t="s">
+      <c r="A2" s="40"/>
+      <c r="B2" s="40"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="50"/>
-      <c r="F2" s="50"/>
-      <c r="G2" s="50"/>
-      <c r="H2" s="50"/>
-      <c r="I2" s="51"/>
+      <c r="E2" s="43"/>
+      <c r="F2" s="43"/>
+      <c r="G2" s="43"/>
+      <c r="H2" s="43"/>
+      <c r="I2" s="44"/>
     </row>
     <row r="3" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="47"/>
-      <c r="B3" s="47"/>
-      <c r="C3" s="47"/>
-      <c r="D3" s="52" t="s">
+      <c r="A3" s="40"/>
+      <c r="B3" s="40"/>
+      <c r="C3" s="40"/>
+      <c r="D3" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="53"/>
-      <c r="F3" s="53"/>
-      <c r="G3" s="53"/>
-      <c r="H3" s="53"/>
-      <c r="I3" s="54"/>
+      <c r="E3" s="46"/>
+      <c r="F3" s="46"/>
+      <c r="G3" s="46"/>
+      <c r="H3" s="46"/>
+      <c r="I3" s="47"/>
     </row>
     <row r="4" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="47"/>
-      <c r="B4" s="47"/>
-      <c r="C4" s="47"/>
-      <c r="D4" s="55" t="s">
+      <c r="A4" s="40"/>
+      <c r="B4" s="40"/>
+      <c r="C4" s="40"/>
+      <c r="D4" s="48" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="56"/>
-      <c r="F4" s="56"/>
-      <c r="G4" s="56"/>
-      <c r="H4" s="56"/>
-      <c r="I4" s="57"/>
+      <c r="E4" s="49"/>
+      <c r="F4" s="49"/>
+      <c r="G4" s="49"/>
+      <c r="H4" s="49"/>
+      <c r="I4" s="50"/>
     </row>
     <row r="5" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="40" t="s">
+      <c r="A5" s="51" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="40"/>
-      <c r="C5" s="40"/>
-      <c r="D5" s="41"/>
-      <c r="E5" s="41"/>
-      <c r="F5" s="41"/>
-      <c r="G5" s="41"/>
-      <c r="H5" s="41"/>
-      <c r="I5" s="41"/>
+      <c r="B5" s="51"/>
+      <c r="C5" s="51"/>
+      <c r="D5" s="52"/>
+      <c r="E5" s="52"/>
+      <c r="F5" s="52"/>
+      <c r="G5" s="52"/>
+      <c r="H5" s="52"/>
+      <c r="I5" s="52"/>
     </row>
     <row r="6" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="43" t="s">
+      <c r="A6" s="54" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="43"/>
-      <c r="C6" s="43"/>
-      <c r="D6" s="43"/>
+      <c r="B6" s="54"/>
+      <c r="C6" s="54"/>
+      <c r="D6" s="54"/>
       <c r="E6" s="22"/>
       <c r="F6" s="20"/>
       <c r="G6" s="20"/>
       <c r="H6" s="20"/>
       <c r="I6" s="32" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="43" t="s">
+      <c r="A7" s="54" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="43"/>
-      <c r="C7" s="43"/>
-      <c r="D7" s="43"/>
+      <c r="B7" s="54"/>
+      <c r="C7" s="54"/>
+      <c r="D7" s="54"/>
       <c r="E7" s="22"/>
       <c r="F7" s="21"/>
       <c r="G7" s="21"/>
@@ -996,12 +996,12 @@
       <c r="I7" s="21"/>
     </row>
     <row r="8" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="43" t="s">
+      <c r="A8" s="54" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="43"/>
-      <c r="C8" s="43"/>
-      <c r="D8" s="43"/>
+      <c r="B8" s="54"/>
+      <c r="C8" s="54"/>
+      <c r="D8" s="54"/>
       <c r="E8" s="22"/>
       <c r="F8" s="20"/>
       <c r="G8" s="20"/>
@@ -1009,12 +1009,12 @@
       <c r="I8" s="20"/>
     </row>
     <row r="9" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="43" t="s">
+      <c r="A9" s="54" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="43"/>
-      <c r="C9" s="43"/>
-      <c r="D9" s="43"/>
+      <c r="B9" s="54"/>
+      <c r="C9" s="54"/>
+      <c r="D9" s="54"/>
       <c r="E9" s="22"/>
       <c r="F9" s="20"/>
       <c r="G9" s="20"/>
@@ -1051,7 +1051,7 @@
       </c>
       <c r="J10" s="7"/>
     </row>
-    <row r="11" spans="1:10" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="36">
         <v>1</v>
       </c>
@@ -1059,7 +1059,7 @@
         <v>23</v>
       </c>
       <c r="C11" s="39" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D11" s="37" t="s">
         <v>24</v>
@@ -1068,13 +1068,13 @@
         <v>21</v>
       </c>
       <c r="F11" s="37" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G11" s="37" t="s">
+        <v>26</v>
+      </c>
+      <c r="H11" s="37" t="s">
         <v>27</v>
-      </c>
-      <c r="H11" s="37" t="s">
-        <v>28</v>
       </c>
       <c r="I11" s="38"/>
       <c r="J11" s="7"/>
@@ -1103,34 +1103,34 @@
       <c r="I13" s="27"/>
     </row>
     <row r="14" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="44" t="s">
+      <c r="A14" s="55" t="s">
         <v>19</v>
       </c>
-      <c r="B14" s="44"/>
-      <c r="C14" s="44"/>
-      <c r="D14" s="44"/>
+      <c r="B14" s="55"/>
+      <c r="C14" s="55"/>
+      <c r="D14" s="55"/>
       <c r="E14" s="15"/>
       <c r="F14" s="13"/>
-      <c r="G14" s="46" t="s">
+      <c r="G14" s="57" t="s">
         <v>20</v>
       </c>
-      <c r="H14" s="46"/>
-      <c r="I14" s="46"/>
+      <c r="H14" s="57"/>
+      <c r="I14" s="57"/>
     </row>
     <row r="15" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="45" t="s">
+      <c r="A15" s="56" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="45"/>
-      <c r="C15" s="45"/>
-      <c r="D15" s="45"/>
+      <c r="B15" s="56"/>
+      <c r="C15" s="56"/>
+      <c r="D15" s="56"/>
       <c r="E15" s="26"/>
       <c r="F15" s="25"/>
-      <c r="G15" s="45" t="s">
+      <c r="G15" s="56" t="s">
         <v>13</v>
       </c>
-      <c r="H15" s="45"/>
-      <c r="I15" s="45"/>
+      <c r="H15" s="56"/>
+      <c r="I15" s="56"/>
     </row>
     <row r="16" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="28"/>
@@ -1188,19 +1188,19 @@
       <c r="I20" s="17"/>
     </row>
     <row r="21" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="44" t="s">
+      <c r="A21" s="55" t="s">
         <v>5</v>
       </c>
-      <c r="B21" s="44"/>
-      <c r="C21" s="44"/>
-      <c r="D21" s="44"/>
+      <c r="B21" s="55"/>
+      <c r="C21" s="55"/>
+      <c r="D21" s="55"/>
       <c r="E21" s="15"/>
       <c r="F21" s="11"/>
-      <c r="G21" s="44" t="s">
+      <c r="G21" s="55" t="s">
         <v>5</v>
       </c>
-      <c r="H21" s="44"/>
-      <c r="I21" s="44"/>
+      <c r="H21" s="55"/>
+      <c r="I21" s="55"/>
     </row>
     <row r="22" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="11"/>
@@ -1214,17 +1214,12 @@
       <c r="I22" s="19"/>
     </row>
     <row r="24" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="B24" s="42"/>
-      <c r="C24" s="42"/>
+      <c r="B24" s="53"/>
+      <c r="C24" s="53"/>
     </row>
     <row r="63" ht="20.25" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="D1:I1"/>
-    <mergeCell ref="D2:I2"/>
-    <mergeCell ref="D3:I3"/>
-    <mergeCell ref="D4:I4"/>
     <mergeCell ref="A5:I5"/>
     <mergeCell ref="B24:C24"/>
     <mergeCell ref="A6:D6"/>
@@ -1237,6 +1232,11 @@
     <mergeCell ref="G14:I14"/>
     <mergeCell ref="G15:I15"/>
     <mergeCell ref="G21:I21"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D1:I1"/>
+    <mergeCell ref="D2:I2"/>
+    <mergeCell ref="D3:I3"/>
+    <mergeCell ref="D4:I4"/>
   </mergeCells>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" scale="95" orientation="landscape" r:id="rId1"/>
